--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output4.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output4.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,6 +518,11 @@
           <t>Is_Anomaly</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Anomaly_Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -565,13 +570,18 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.0001529579205381523</v>
+        <v>4.661641188320533e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -620,13 +630,18 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.01643891793329244</v>
+        <v>0.01073420807760463</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -675,13 +690,18 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.0003968301745547719</v>
+        <v>0.0001387267620917825</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -730,13 +750,18 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0.0001352074781833172</v>
+        <v>4.468046159779203e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -785,13 +810,18 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0.0001352074781833172</v>
+        <v>4.468046159779203e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -840,13 +870,18 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>0.0001159806826172156</v>
+        <v>4.657046053781918e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -895,13 +930,18 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.0008383026572151451</v>
+        <v>0.0001486416260167276</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -950,13 +990,18 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0.0001323934439559773</v>
+        <v>4.426195613531074e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1005,13 +1050,18 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0.0001323934439559773</v>
+        <v>4.426195613531074e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1060,13 +1110,18 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>0.0001023720858555253</v>
+        <v>4.145934742792224e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1115,13 +1170,18 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.0002738567600990144</v>
+        <v>0.0001070474497299978</v>
       </c>
       <c r="P12" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1170,13 +1230,18 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0.0001127686899649944</v>
+        <v>4.904956545358539e-05</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1225,13 +1290,18 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0.0004301758745069706</v>
+        <v>5.780652330541369e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1280,13 +1350,18 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>0.0001332572555106285</v>
+        <v>5.88231793629986e-05</v>
       </c>
       <c r="P15" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1335,13 +1410,18 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.0001055766972495887</v>
+        <v>4.902330874357904e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1390,13 +1470,18 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.000132583178299529</v>
+        <v>4.505939095587601e-05</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1445,13 +1530,18 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0.0001144600295714667</v>
+        <v>4.692633596966184e-05</v>
       </c>
       <c r="P18" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1500,13 +1590,18 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0.0001091230926196706</v>
+        <v>4.7696464513411e-05</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1555,13 +1650,18 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>9.056324375417861e-05</v>
+        <v>5.59298449115293e-05</v>
       </c>
       <c r="P20" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1610,13 +1710,18 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.0003288444860669837</v>
+        <v>0.0001128080719781425</v>
       </c>
       <c r="P21" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1665,13 +1770,18 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0.0001393182889934395</v>
+        <v>4.406911157706774e-05</v>
       </c>
       <c r="P22" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1720,13 +1830,18 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0.000210050294911255</v>
+        <v>5.418429650349664e-05</v>
       </c>
       <c r="P23" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1775,13 +1890,18 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.0001254754239239517</v>
+        <v>5.801272957848062e-05</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1830,13 +1950,18 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0.0001697968403270278</v>
+        <v>7.508918963933257e-05</v>
       </c>
       <c r="P25" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1885,13 +2010,18 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.0001673729724275191</v>
+        <v>0.0001403788687496988</v>
       </c>
       <c r="P26" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1940,13 +2070,18 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.0002921160572712733</v>
+        <v>0.0001425083527682633</v>
       </c>
       <c r="P27" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1995,13 +2130,18 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0.0001466134548783442</v>
+        <v>6.963172506569487e-05</v>
       </c>
       <c r="P28" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2050,13 +2190,18 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0.0001523685717776053</v>
+        <v>8.908301302324871e-05</v>
       </c>
       <c r="P29" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2105,13 +2250,18 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0.0001357102888266181</v>
+        <v>7.440618389440349e-05</v>
       </c>
       <c r="P30" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2160,13 +2310,18 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.0002961789761076086</v>
+        <v>0.0002263060345611325</v>
       </c>
       <c r="P31" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2215,13 +2370,18 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.0002708604290147757</v>
+        <v>0.0002249621742749904</v>
       </c>
       <c r="P32" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2270,13 +2430,18 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.0001696856142574964</v>
+        <v>0.0001793649888768791</v>
       </c>
       <c r="P33" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2325,13 +2490,18 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.0006962736684494794</v>
+        <v>0.0001814688955276196</v>
       </c>
       <c r="P34" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2380,13 +2550,18 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>0.0004858678456741312</v>
+        <v>9.118204374428444e-05</v>
       </c>
       <c r="P35" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2435,13 +2610,18 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0.0004310564042319537</v>
+        <v>9.949204412783313e-05</v>
       </c>
       <c r="P36" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2490,13 +2670,18 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.001375997006892431</v>
+        <v>0.0001062156558489331</v>
       </c>
       <c r="P37" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2545,13 +2730,18 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.001980253279016147</v>
+        <v>0.0005978242879728075</v>
       </c>
       <c r="P38" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2600,13 +2790,18 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.002108077198058032</v>
+        <v>0.0005910704978404815</v>
       </c>
       <c r="P39" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2655,13 +2850,18 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>0.0005253972040384194</v>
+        <v>7.587855455091817e-05</v>
       </c>
       <c r="P40" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2710,13 +2910,18 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.001034422474895505</v>
+        <v>0.0001051057531091821</v>
       </c>
       <c r="P41" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2765,13 +2970,18 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.0007229128195514111</v>
+        <v>0.0004354547524807643</v>
       </c>
       <c r="P42" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2820,13 +3030,18 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.0006247598607113998</v>
+        <v>0.0001035835808343427</v>
       </c>
       <c r="P43" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2875,13 +3090,18 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0.0006275879721172195</v>
+        <v>7.190595211002633e-05</v>
       </c>
       <c r="P44" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2930,13 +3150,18 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.0002304158036728072</v>
+        <v>6.225913975251176e-05</v>
       </c>
       <c r="P45" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2985,13 +3210,18 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.0004129329382228708</v>
+        <v>0.0001460485289522703</v>
       </c>
       <c r="P46" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -3040,13 +3270,18 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.000423159677597488</v>
+        <v>5.292379942772844e-05</v>
       </c>
       <c r="P47" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3095,13 +3330,18 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0.0003813244913870624</v>
+        <v>5.184441312364169e-05</v>
       </c>
       <c r="P48" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q48" t="b">
         <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3150,13 +3390,18 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>0.0001614048731228154</v>
+        <v>6.579840874163114e-05</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3205,13 +3450,18 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.0004061588615362721</v>
+        <v>0.0001370346596981094</v>
       </c>
       <c r="P50" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3260,13 +3510,18 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>0.0002035724083938351</v>
+        <v>8.051354116275642e-05</v>
       </c>
       <c r="P51" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3315,13 +3570,18 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.0001859334924848934</v>
+        <v>7.505139544461118e-05</v>
       </c>
       <c r="P52" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3370,13 +3630,18 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.0002482425442499263</v>
+        <v>9.785852466989314e-05</v>
       </c>
       <c r="P53" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3425,13 +3690,18 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.0002148528185702194</v>
+        <v>8.582343753713286e-05</v>
       </c>
       <c r="P54" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3480,13 +3750,18 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.0002203262234749663</v>
+        <v>8.101376425187327e-05</v>
       </c>
       <c r="P55" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3535,13 +3810,18 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.0003897865331941443</v>
+        <v>0.000228480072735836</v>
       </c>
       <c r="P56" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3590,13 +3870,18 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>0.0001817585498903755</v>
+        <v>6.601556402871563e-05</v>
       </c>
       <c r="P57" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3645,13 +3930,18 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.0005395335333955742</v>
+        <v>0.0004062358189492137</v>
       </c>
       <c r="P58" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3700,13 +3990,18 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>0.0002275729705980861</v>
+        <v>9.812895341392193e-05</v>
       </c>
       <c r="P59" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3755,13 +4050,18 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.0004452206899129953</v>
+        <v>0.0003297365367620753</v>
       </c>
       <c r="P60" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3810,13 +4110,18 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.0003615170310367862</v>
+        <v>0.0002656822395525806</v>
       </c>
       <c r="P61" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3865,13 +4170,18 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0.0001298952840105375</v>
+        <v>4.497541656576091e-05</v>
       </c>
       <c r="P62" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3920,13 +4230,18 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>0.0001347880699812518</v>
+        <v>6.738884326839912e-05</v>
       </c>
       <c r="P63" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -3975,13 +4290,18 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0.00119535636158253</v>
+        <v>0.0001522210852890404</v>
       </c>
       <c r="P64" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -4030,13 +4350,18 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0.001144669367373688</v>
+        <v>0.0003392913941150041</v>
       </c>
       <c r="P65" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4085,13 +4410,18 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.001236980128104434</v>
+        <v>0.0003573300794722739</v>
       </c>
       <c r="P66" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4140,13 +4470,18 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>0.0001144600295714667</v>
+        <v>4.692633596966184e-05</v>
       </c>
       <c r="P67" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4195,13 +4530,18 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.0001085243170423832</v>
+        <v>5.056866195617257e-05</v>
       </c>
       <c r="P68" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4250,13 +4590,18 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.0001829146850586679</v>
+        <v>5.038570117111988e-05</v>
       </c>
       <c r="P69" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4305,13 +4650,18 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.0001420100016315387</v>
+        <v>4.419714593329009e-05</v>
       </c>
       <c r="P70" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4360,13 +4710,18 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.0001168873604984543</v>
+        <v>5.517709072491116e-05</v>
       </c>
       <c r="P71" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4415,13 +4770,18 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>0.0002609668175972186</v>
+        <v>9.650932896649773e-05</v>
       </c>
       <c r="P72" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q72" t="b">
         <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4470,13 +4830,18 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.0001546022314906106</v>
+        <v>0.0001213323256417355</v>
       </c>
       <c r="P73" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q73" t="b">
         <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4525,13 +4890,18 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>0.0001367949636966313</v>
+        <v>4.416558199754655e-05</v>
       </c>
       <c r="P74" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q74" t="b">
         <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4580,13 +4950,18 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>0.0001172863260427701</v>
+        <v>5.029882941275956e-05</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q75" t="b">
         <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4635,13 +5010,18 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0.00101997245277292</v>
+        <v>0.0001141622013627488</v>
       </c>
       <c r="P76" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q76" t="b">
         <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -4690,13 +5070,18 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.0001768532893798858</v>
+        <v>4.432790890061883e-05</v>
       </c>
       <c r="P77" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4745,13 +5130,18 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>0.0001476715720880268</v>
+        <v>4.524356827853671e-05</v>
       </c>
       <c r="P78" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4800,13 +5190,18 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.00101997245277292</v>
+        <v>0.0001141622013627488</v>
       </c>
       <c r="P79" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4855,13 +5250,18 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.0009963577281076616</v>
+        <v>6.306854504476227e-05</v>
       </c>
       <c r="P80" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -4910,13 +5310,18 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.000259098768333122</v>
+        <v>3.709784770224023e-05</v>
       </c>
       <c r="P81" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4965,13 +5370,18 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.06004913009822775</v>
+        <v>0.004590283741878276</v>
       </c>
       <c r="P82" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q82" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -5020,13 +5430,18 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>0.0002501625748647491</v>
+        <v>6.24268905365967e-05</v>
       </c>
       <c r="P83" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -5075,13 +5490,18 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.0003183965217037117</v>
+        <v>6.966484122978417e-05</v>
       </c>
       <c r="P84" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q84" t="b">
         <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5130,13 +5550,18 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.0004380502873410458</v>
+        <v>6.136613615396005e-05</v>
       </c>
       <c r="P85" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5185,13 +5610,18 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.0004380502873410458</v>
+        <v>6.136613615396005e-05</v>
       </c>
       <c r="P86" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5240,13 +5670,18 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0.0004380502873410458</v>
+        <v>6.136613615396005e-05</v>
       </c>
       <c r="P87" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5295,13 +5730,18 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.0005291561839124899</v>
+        <v>0.0001181221920041625</v>
       </c>
       <c r="P88" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5350,13 +5790,18 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.001042183207041095</v>
+        <v>0.0002068515316868029</v>
       </c>
       <c r="P89" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5405,13 +5850,18 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.0003373560617112784</v>
+        <v>4.926597947788053e-05</v>
       </c>
       <c r="P90" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q90" t="b">
         <v>0</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5460,13 +5910,18 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.001655619244890361</v>
+        <v>0.0003377080719487111</v>
       </c>
       <c r="P91" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q91" t="b">
         <v>0</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5515,13 +5970,18 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.001161171272674285</v>
+        <v>0.0003132924218856318</v>
       </c>
       <c r="P92" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5570,13 +6030,18 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.01024298252059739</v>
+        <v>0.002692820783242889</v>
       </c>
       <c r="P93" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -5625,13 +6090,18 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.0001733833735775622</v>
+        <v>3.84528161824115e-05</v>
       </c>
       <c r="P94" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -5680,13 +6150,18 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.0004533332381796218</v>
+        <v>0.0001427690821744507</v>
       </c>
       <c r="P95" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q95" t="b">
         <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5735,13 +6210,18 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.0004498466662438369</v>
+        <v>6.572597530670648e-05</v>
       </c>
       <c r="P96" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q96" t="b">
         <v>0</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5790,13 +6270,18 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.0004427332260102188</v>
+        <v>6.002085665883255e-05</v>
       </c>
       <c r="P97" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q97" t="b">
         <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5845,13 +6330,18 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.00136089637681931</v>
+        <v>0.001088928217204538</v>
       </c>
       <c r="P98" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -5900,13 +6390,18 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.001730197014484376</v>
+        <v>0.001260828807986957</v>
       </c>
       <c r="P99" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5955,13 +6450,18 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.0001834516005588039</v>
+        <v>8.279480225214082e-05</v>
       </c>
       <c r="P100" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -6010,13 +6510,18 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.001548157529090788</v>
+        <v>0.001171087311578488</v>
       </c>
       <c r="P101" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -6065,13 +6570,18 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.0001603132714144669</v>
+        <v>5.438664389180259e-05</v>
       </c>
       <c r="P102" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q102" t="b">
         <v>0</v>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6120,13 +6630,18 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.0009561424105546573</v>
+        <v>0.001017711010788485</v>
       </c>
       <c r="P103" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q103" t="b">
         <v>0</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -6175,13 +6690,18 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.001910869464495668</v>
+        <v>0.001405182172686864</v>
       </c>
       <c r="P104" t="n">
-        <v>0.01850526721287616</v>
+        <v>0.006429952688328516</v>
       </c>
       <c r="Q104" t="b">
         <v>0</v>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output4.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output4.xlsx
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4.661641188320533e-05</v>
+        <v>4.226525414355662e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
@@ -630,17 +630,17 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.01073420807760463</v>
+        <v>0.0043543674287103</v>
       </c>
       <c r="P3" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>⚠️ Anomaly</t>
+          <t>✅ Normal</t>
         </is>
       </c>
     </row>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.0001387267620917825</v>
+        <v>9.311426904473987e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4.468046159779203e-05</v>
+        <v>4.35694087217983e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>4.468046159779203e-05</v>
+        <v>4.35694087217983e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4.657046053781918e-05</v>
+        <v>4.483645222943447e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0.0001486416260167276</v>
+        <v>0.0001400851966246853</v>
       </c>
       <c r="P8" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>4.426195613531074e-05</v>
+        <v>4.470161124493001e-05</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q9" t="b">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>4.426195613531074e-05</v>
+        <v>4.470161124493001e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>4.145934742792224e-05</v>
+        <v>4.199082170782285e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0.0001070474497299978</v>
+        <v>4.66967899178407e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>4.904956545358539e-05</v>
+        <v>4.780853938582928e-05</v>
       </c>
       <c r="P13" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>5.780652330541369e-05</v>
+        <v>5.699070182851696e-05</v>
       </c>
       <c r="P14" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>5.88231793629986e-05</v>
+        <v>5.136092291874383e-05</v>
       </c>
       <c r="P15" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>4.902330874357904e-05</v>
+        <v>4.315965366950134e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q16" t="b">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>4.505939095587601e-05</v>
+        <v>4.828896415595687e-05</v>
       </c>
       <c r="P17" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>4.692633596966184e-05</v>
+        <v>4.854852900991812e-05</v>
       </c>
       <c r="P18" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q18" t="b">
         <v>0</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4.7696464513411e-05</v>
+        <v>4.291187850682869e-05</v>
       </c>
       <c r="P19" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>5.59298449115293e-05</v>
+        <v>4.332359703418323e-05</v>
       </c>
       <c r="P20" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>0.0001128080719781425</v>
+        <v>5.146755615721073e-05</v>
       </c>
       <c r="P21" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>4.406911157706774e-05</v>
+        <v>4.733848623040922e-05</v>
       </c>
       <c r="P22" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q22" t="b">
         <v>0</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>5.418429650349664e-05</v>
+        <v>5.564229751104306e-05</v>
       </c>
       <c r="P23" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>5.801272957848062e-05</v>
+        <v>4.820735674776804e-05</v>
       </c>
       <c r="P24" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>7.508918963933257e-05</v>
+        <v>4.902663233464314e-05</v>
       </c>
       <c r="P25" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q25" t="b">
         <v>0</v>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.0001403788687496988</v>
+        <v>7.100552601863131e-05</v>
       </c>
       <c r="P26" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0.0001425083527682633</v>
+        <v>0.0001363651549083424</v>
       </c>
       <c r="P27" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -2130,10 +2130,10 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>6.963172506569487e-05</v>
+        <v>8.64372362130085e-05</v>
       </c>
       <c r="P28" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>8.908301302324871e-05</v>
+        <v>8.725854175257569e-05</v>
       </c>
       <c r="P29" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q29" t="b">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>7.440618389440349e-05</v>
+        <v>7.428232784408751e-05</v>
       </c>
       <c r="P30" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q30" t="b">
         <v>0</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0.0002263060345611325</v>
+        <v>0.0004423255570696776</v>
       </c>
       <c r="P31" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0.0002249621742749904</v>
+        <v>0.0004421399800918795</v>
       </c>
       <c r="P32" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0.0001793649888768791</v>
+        <v>0.0003044879574148094</v>
       </c>
       <c r="P33" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0.0001814688955276196</v>
+        <v>0.0002340857215187598</v>
       </c>
       <c r="P34" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>9.118204374428444e-05</v>
+        <v>0.0001166362801372673</v>
       </c>
       <c r="P35" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>9.949204412783313e-05</v>
+        <v>0.0001161153967657127</v>
       </c>
       <c r="P36" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0.0001062156558489331</v>
+        <v>0.000161898303355096</v>
       </c>
       <c r="P37" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.0005978242879728075</v>
+        <v>0.0001498425980526505</v>
       </c>
       <c r="P38" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0.0005910704978404815</v>
+        <v>0.0001502073545346699</v>
       </c>
       <c r="P39" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q39" t="b">
         <v>0</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>7.587855455091817e-05</v>
+        <v>8.397438113807689e-05</v>
       </c>
       <c r="P40" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>0.0001051057531091821</v>
+        <v>7.588523410756663e-05</v>
       </c>
       <c r="P41" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
@@ -2970,10 +2970,10 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>0.0004354547524807643</v>
+        <v>0.0001385733662863484</v>
       </c>
       <c r="P42" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q42" t="b">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>0.0001035835808343427</v>
+        <v>0.000185603851144239</v>
       </c>
       <c r="P43" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
@@ -3090,10 +3090,10 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>7.190595211002633e-05</v>
+        <v>0.0001557957423249075</v>
       </c>
       <c r="P44" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>6.225913975251176e-05</v>
+        <v>7.058640955272309e-05</v>
       </c>
       <c r="P45" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q45" t="b">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0.0001460485289522703</v>
+        <v>0.0001101540454292694</v>
       </c>
       <c r="P46" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>5.292379942772844e-05</v>
+        <v>7.002372347890758e-05</v>
       </c>
       <c r="P47" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>5.184441312364169e-05</v>
+        <v>6.129870178531859e-05</v>
       </c>
       <c r="P48" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q48" t="b">
         <v>0</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="O49" t="n">
-        <v>6.579840874163114e-05</v>
+        <v>5.407364753282366e-05</v>
       </c>
       <c r="P49" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q49" t="b">
         <v>0</v>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>0.0001370346596981094</v>
+        <v>5.545406835195708e-05</v>
       </c>
       <c r="P50" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="O51" t="n">
-        <v>8.051354116275642e-05</v>
+        <v>5.522240897277871e-05</v>
       </c>
       <c r="P51" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="O52" t="n">
-        <v>7.505139544461118e-05</v>
+        <v>5.419210176592739e-05</v>
       </c>
       <c r="P52" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="O53" t="n">
-        <v>9.785852466989314e-05</v>
+        <v>9.270557302970852e-05</v>
       </c>
       <c r="P53" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
@@ -3690,10 +3690,10 @@
         </is>
       </c>
       <c r="O54" t="n">
-        <v>8.582343753713286e-05</v>
+        <v>5.998926368641463e-05</v>
       </c>
       <c r="P54" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>8.101376425187327e-05</v>
+        <v>4.591411378731739e-05</v>
       </c>
       <c r="P55" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.000228480072735836</v>
+        <v>0.000120129305304764</v>
       </c>
       <c r="P56" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>6.601556402871563e-05</v>
+        <v>4.815842611122546e-05</v>
       </c>
       <c r="P57" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
@@ -3930,10 +3930,10 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>0.0004062358189492137</v>
+        <v>0.0001059700960081412</v>
       </c>
       <c r="P58" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
@@ -3990,10 +3990,10 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>9.812895341392193e-05</v>
+        <v>8.21592327610273e-05</v>
       </c>
       <c r="P59" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
@@ -4050,10 +4050,10 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.0003297365367620753</v>
+        <v>4.563670594131183e-05</v>
       </c>
       <c r="P60" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.0002656822395525806</v>
+        <v>4.404998932390382e-05</v>
       </c>
       <c r="P61" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>4.497541656576091e-05</v>
+        <v>4.673077550684175e-05</v>
       </c>
       <c r="P62" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>6.738884326839912e-05</v>
+        <v>4.77364040493802e-05</v>
       </c>
       <c r="P63" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>0.0001522210852890404</v>
+        <v>0.0001541070970144849</v>
       </c>
       <c r="P64" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q64" t="b">
         <v>0</v>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0.0003392913941150041</v>
+        <v>0.0001302665898260373</v>
       </c>
       <c r="P65" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.0003573300794722739</v>
+        <v>0.0001299234266258001</v>
       </c>
       <c r="P66" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
@@ -4470,10 +4470,10 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>4.692633596966184e-05</v>
+        <v>4.854852900991812e-05</v>
       </c>
       <c r="P67" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q67" t="b">
         <v>0</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="O68" t="n">
-        <v>5.056866195617257e-05</v>
+        <v>4.883032201618383e-05</v>
       </c>
       <c r="P68" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q68" t="b">
         <v>0</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>5.038570117111988e-05</v>
+        <v>5.481740868122812e-05</v>
       </c>
       <c r="P69" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q69" t="b">
         <v>0</v>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>4.419714593329009e-05</v>
+        <v>4.682658932368748e-05</v>
       </c>
       <c r="P70" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="O71" t="n">
-        <v>5.517709072491116e-05</v>
+        <v>4.875143921071883e-05</v>
       </c>
       <c r="P71" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="O72" t="n">
-        <v>9.650932896649773e-05</v>
+        <v>5.04902748478174e-05</v>
       </c>
       <c r="P72" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q72" t="b">
         <v>0</v>
@@ -4830,10 +4830,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0.0001213323256417355</v>
+        <v>7.479323449959875e-05</v>
       </c>
       <c r="P73" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q73" t="b">
         <v>0</v>
@@ -4890,10 +4890,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>4.416558199754655e-05</v>
+        <v>4.783851196887632e-05</v>
       </c>
       <c r="P74" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q74" t="b">
         <v>0</v>
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="O75" t="n">
-        <v>5.029882941275956e-05</v>
+        <v>4.711802992794045e-05</v>
       </c>
       <c r="P75" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q75" t="b">
         <v>0</v>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0.0001141622013627488</v>
+        <v>4.736974096545087e-05</v>
       </c>
       <c r="P76" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q76" t="b">
         <v>0</v>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>4.432790890061883e-05</v>
+        <v>4.620408635093259e-05</v>
       </c>
       <c r="P77" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>4.524356827853671e-05</v>
+        <v>4.655284078544838e-05</v>
       </c>
       <c r="P78" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>0.0001141622013627488</v>
+        <v>4.736974096545087e-05</v>
       </c>
       <c r="P79" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
@@ -5250,10 +5250,10 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>6.306854504476227e-05</v>
+        <v>4.714290295620649e-05</v>
       </c>
       <c r="P80" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>3.709784770224023e-05</v>
+        <v>4.299560776975293e-05</v>
       </c>
       <c r="P81" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q81" t="b">
         <v>0</v>
@@ -5370,10 +5370,10 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.004590283741878276</v>
+        <v>0.002772435812540687</v>
       </c>
       <c r="P82" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>6.24268905365967e-05</v>
+        <v>5.817480320013706e-05</v>
       </c>
       <c r="P83" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
@@ -5490,10 +5490,10 @@
         </is>
       </c>
       <c r="O84" t="n">
-        <v>6.966484122978417e-05</v>
+        <v>5.675415002169999e-05</v>
       </c>
       <c r="P84" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q84" t="b">
         <v>0</v>
@@ -5550,10 +5550,10 @@
         </is>
       </c>
       <c r="O85" t="n">
-        <v>6.136613615396005e-05</v>
+        <v>4.681685182367546e-05</v>
       </c>
       <c r="P85" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>6.136613615396005e-05</v>
+        <v>4.681685182367546e-05</v>
       </c>
       <c r="P86" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>6.136613615396005e-05</v>
+        <v>4.681685182367546e-05</v>
       </c>
       <c r="P87" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>0.0001181221920041625</v>
+        <v>7.26359722366276e-05</v>
       </c>
       <c r="P88" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.0002068515316868029</v>
+        <v>4.462486486100418e-05</v>
       </c>
       <c r="P89" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="O90" t="n">
-        <v>4.926597947788053e-05</v>
+        <v>4.142830754180407e-05</v>
       </c>
       <c r="P90" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q90" t="b">
         <v>0</v>
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.0003377080719487111</v>
+        <v>4.345856030126863e-05</v>
       </c>
       <c r="P91" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q91" t="b">
         <v>0</v>
@@ -5970,10 +5970,10 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.0003132924218856318</v>
+        <v>4.602054449858301e-05</v>
       </c>
       <c r="P92" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.002692820783242889</v>
+        <v>0.0008566609613235577</v>
       </c>
       <c r="P93" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q93" t="b">
         <v>0</v>
@@ -6090,10 +6090,10 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>3.84528161824115e-05</v>
+        <v>4.343819132743108e-05</v>
       </c>
       <c r="P94" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q94" t="b">
         <v>0</v>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.0001427690821744507</v>
+        <v>7.718411771117262e-05</v>
       </c>
       <c r="P95" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q95" t="b">
         <v>0</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>6.572597530670648e-05</v>
+        <v>5.59868320992305e-05</v>
       </c>
       <c r="P96" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q96" t="b">
         <v>0</v>
@@ -6270,10 +6270,10 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>6.002085665883255e-05</v>
+        <v>5.168108108610779e-05</v>
       </c>
       <c r="P97" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q97" t="b">
         <v>0</v>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.001088928217204538</v>
+        <v>0.0003321403553894254</v>
       </c>
       <c r="P98" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q98" t="b">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.001260828807986957</v>
+        <v>6.126242280286075e-05</v>
       </c>
       <c r="P99" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q99" t="b">
         <v>0</v>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>8.279480225214082e-05</v>
+        <v>0.000110949776382677</v>
       </c>
       <c r="P100" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q100" t="b">
         <v>0</v>
@@ -6510,10 +6510,10 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.001171087311578488</v>
+        <v>0.0001105603584032015</v>
       </c>
       <c r="P101" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q101" t="b">
         <v>0</v>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>5.438664389180259e-05</v>
+        <v>8.247623663898021e-05</v>
       </c>
       <c r="P102" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q102" t="b">
         <v>0</v>
@@ -6630,10 +6630,10 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.001017711010788485</v>
+        <v>0.0003871562397230603</v>
       </c>
       <c r="P103" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q103" t="b">
         <v>0</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.001405182172686864</v>
+        <v>5.881545659592539e-05</v>
       </c>
       <c r="P104" t="n">
-        <v>0.006429952688328516</v>
+        <v>0.004703492137431826</v>
       </c>
       <c r="Q104" t="b">
         <v>0</v>
